--- a/output/2026-09-30/enriched_analysis.xlsx
+++ b/output/2026-09-30/enriched_analysis.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.313</v>
+        <v>3.314</v>
       </c>
       <c r="W2" t="n">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="X2" t="n">
         <v>22.7</v>
@@ -1164,7 +1164,7 @@
         <v>0.05</v>
       </c>
       <c r="W3" t="n">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="X3" t="n">
         <v>9.199999999999999</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.923</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="X4" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
@@ -1553,16 +1553,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
         <v>17</v>
@@ -1582,28 +1582,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>68.37</v>
+        <v>5204.5</v>
       </c>
       <c r="J5" t="n">
-        <v>74.22</v>
+        <v>5198.76</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.9</v>
+        <v>0.1</v>
       </c>
       <c r="L5" t="n">
-        <v>72.56999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="M5" t="n">
-        <v>2.01</v>
+        <v>7.21</v>
       </c>
       <c r="N5" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1617,60 +1617,60 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.003</v>
+        <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>200</v>
+        <v>16177</v>
       </c>
       <c r="X5" t="n">
-        <v>8.48</v>
+        <v>41.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.97</v>
+        <v>145</v>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.73</v>
+        <v>27.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>13.6</v>
+        <v>25.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.86</v>
+        <v>0.64</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.140000000000001</v>
+        <v>5</v>
       </c>
       <c r="AG5" t="n">
-        <v>65.04000000000001</v>
+        <v>5463.92</v>
       </c>
       <c r="AH5" t="n">
-        <v>53.06</v>
+        <v>4475.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>49.1</v>
+        <v>44.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>74.21830535305453</v>
+        <v>5198.755988455989</v>
       </c>
       <c r="AK5" t="n">
-        <v>-7.9</v>
+        <v>0.1</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1689,52 +1689,52 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1525105</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9663835</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="BC5" t="n">
-        <v>20066329</v>
+        <v>72054758</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1770,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>9663835</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -1785,12 +1785,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1802,107 +1802,107 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>575.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>510.94</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30622049</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>30622049</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>17</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5204.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5198.76</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>67.16</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="N6" t="n">
-        <v>72054758</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>72054758</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.045</v>
+        <v>0.31</v>
       </c>
       <c r="W6" t="n">
-        <v>16183</v>
+        <v>988</v>
       </c>
       <c r="X6" t="n">
-        <v>41.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>27.38</v>
+        <v>14.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>25.5</v>
+        <v>14.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>5463.92</v>
+        <v>509.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>4475.56</v>
+        <v>490.71</v>
       </c>
       <c r="AI6" t="n">
-        <v>44.6</v>
+        <v>34.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5198.755988455989</v>
+        <v>510.9380308010612</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1</v>
+        <v>12.6</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1916,57 +1916,57 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR6" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>9018372</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>24967565</v>
       </c>
       <c r="BB6" t="n">
-        <v>72054758</v>
+        <v>30622049</v>
       </c>
       <c r="BC6" t="n">
-        <v>72054758</v>
+        <v>30622049</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -2002,10 +2002,10 @@
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>24967565</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
@@ -2017,16 +2017,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2034,40 +2034,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>575.5</v>
+        <v>68.37</v>
       </c>
       <c r="J7" t="n">
-        <v>510.94</v>
+        <v>74.22</v>
       </c>
       <c r="K7" t="n">
-        <v>12.6</v>
+        <v>-7.9</v>
       </c>
       <c r="L7" t="n">
-        <v>62.09</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>3.06</v>
+        <v>2.01</v>
       </c>
       <c r="N7" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2081,91 +2081,91 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>21-09-2026</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="W7" t="n">
+        <v>201</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="Y7" t="n">
         <v>17</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="Z7" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>53.06</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>74.21830535305453</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>21-09-2026</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="W7" t="n">
-        <v>980</v>
-      </c>
-      <c r="X7" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>509.85</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>490.71</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>510.9380308010612</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
       <c r="AQ7" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="AR7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AS7" t="n">
         <v>9</v>
@@ -2174,31 +2174,31 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9018372</v>
+        <v>1525105</v>
       </c>
       <c r="BA7" t="n">
-        <v>24967565</v>
+        <v>9663835</v>
       </c>
       <c r="BB7" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="BC7" t="n">
-        <v>30622049</v>
+        <v>20066329</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>24967565</v>
+        <v>9663835</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="W8" t="n">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="X8" t="n">
         <v>22.8</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2.324</v>
+        <v>2.334</v>
       </c>
       <c r="W10" t="n">
-        <v>2526</v>
+        <v>2515</v>
       </c>
       <c r="X10" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y10" t="n">
         <v>6</v>
@@ -3018,10 +3018,10 @@
         <v>0.13</v>
       </c>
       <c r="W11" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="X11" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="Y11" t="n">
         <v>17</v>
@@ -3476,10 +3476,10 @@
         <v>0.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="X13" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>2.852</v>
+        <v>2.86</v>
       </c>
       <c r="W14" t="n">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="X14" t="n">
         <v>25.9</v>
@@ -3934,10 +3934,10 @@
         <v>0.062</v>
       </c>
       <c r="W15" t="n">
-        <v>1777</v>
+        <v>1783</v>
       </c>
       <c r="X15" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>790</v>
+        <v>803</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="Y17" t="n">
         <v>19</v>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="W18" t="n">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="X18" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.502</v>
+        <v>0.503</v>
       </c>
       <c r="W19" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="X19" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="Y19" t="n">
         <v>21</v>
@@ -5092,10 +5092,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>52237</v>
+        <v>52260</v>
       </c>
       <c r="X20" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="Y20" t="n">
         <v>5</v>
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="W21" t="n">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="X21" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="Y21" t="n">
         <v>3</v>
@@ -5345,7 +5345,7 @@
         <v>11.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.897</v>
+        <v>0.91</v>
       </c>
       <c r="W22" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="X22" t="n">
-        <v>6.46</v>
+        <v>6.37</v>
       </c>
       <c r="Y22" t="n">
         <v>31</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="W23" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X23" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.653</v>
+        <v>0.65</v>
       </c>
       <c r="W24" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="X24" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="Y24" t="n">
         <v>19</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="W25" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="X25" t="n">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="Y25" t="n">
         <v>-61</v>
@@ -6473,13 +6473,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.495</v>
+        <v>0.488</v>
       </c>
       <c r="W26" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="X26" t="n">
-        <v>37.6</v>
+        <v>38.1</v>
       </c>
       <c r="Y26" t="n">
         <v>-44</v>
@@ -6708,7 +6708,7 @@
         <v>0.075</v>
       </c>
       <c r="W27" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.276</v>
+        <v>0.275</v>
       </c>
       <c r="W28" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="X28" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Y28" t="n">
         <v>9</v>
@@ -7170,10 +7170,10 @@
         <v>0.051</v>
       </c>
       <c r="W29" t="n">
-        <v>5108</v>
+        <v>5163</v>
       </c>
       <c r="X29" t="n">
-        <v>33.3</v>
+        <v>33.6</v>
       </c>
       <c r="Y29" t="n">
         <v>-25</v>
@@ -7402,7 +7402,7 @@
         <v>0.045</v>
       </c>
       <c r="W30" t="n">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="X30" t="n">
         <v>20.3</v>
@@ -7631,13 +7631,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.802</v>
+        <v>0.804</v>
       </c>
       <c r="W31" t="n">
-        <v>3940</v>
+        <v>3931</v>
       </c>
       <c r="X31" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Y31" t="n">
         <v>2</v>
@@ -8093,10 +8093,10 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.227</v>
+        <v>0.226</v>
       </c>
       <c r="W33" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="X33" t="n">
         <v>13.6</v>
@@ -8325,13 +8325,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.271</v>
+        <v>0.268</v>
       </c>
       <c r="W34" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="X34" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="Y34" t="n">
         <v>16</v>
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="W36" t="n">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="X36" t="n">
         <v>18.4</v>
@@ -9024,7 +9024,7 @@
         <v>0.02</v>
       </c>
       <c r="W37" t="n">
-        <v>9670</v>
+        <v>9672</v>
       </c>
       <c r="X37" t="n">
         <v>12.8</v>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="W39" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="X39" t="n">
-        <v>95.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="Y39" t="n">
         <v>246</v>
@@ -9717,7 +9717,7 @@
         <v>1632</v>
       </c>
       <c r="X40" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="Y40" t="n">
         <v>39</v>
@@ -9946,7 +9946,7 @@
         <v>0.011</v>
       </c>
       <c r="W41" t="n">
-        <v>4148</v>
+        <v>4158</v>
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="n">
@@ -10176,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>4921</v>
+        <v>4916</v>
       </c>
       <c r="X42" t="n">
         <v>11.5</v>
@@ -10405,13 +10405,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="W43" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="X43" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10872,7 +10872,7 @@
         <v>0.075</v>
       </c>
       <c r="W45" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="X45" t="n">
         <v>13.4</v>
@@ -11104,10 +11104,10 @@
         <v>0.126</v>
       </c>
       <c r="W46" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="X46" t="n">
-        <v>6.35</v>
+        <v>6.38</v>
       </c>
       <c r="Y46" t="n">
         <v>118</v>
@@ -11332,7 +11332,7 @@
         <v>0.024</v>
       </c>
       <c r="W47" t="n">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="n">
@@ -11562,10 +11562,10 @@
         <v>0.008</v>
       </c>
       <c r="W48" t="n">
-        <v>5363</v>
+        <v>5381</v>
       </c>
       <c r="X48" t="n">
-        <v>9.06</v>
+        <v>9.09</v>
       </c>
       <c r="Y48" t="n">
         <v>43</v>
@@ -11794,10 +11794,10 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>8871</v>
+        <v>8881</v>
       </c>
       <c r="X49" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="Y49" t="n">
         <v>21</v>
@@ -12026,10 +12026,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3453</v>
+        <v>3449</v>
       </c>
       <c r="X50" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Y50" t="n">
         <v>42</v>
@@ -12255,13 +12255,13 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.215</v>
+        <v>0.214</v>
       </c>
       <c r="W51" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X51" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Y51" t="n">
         <v>21</v>
@@ -12490,7 +12490,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>115240</v>
+        <v>115270</v>
       </c>
       <c r="X52" t="n">
         <v>33.2</v>
@@ -12824,101 +12824,101 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.37</v>
+        <v>5204.5</v>
       </c>
       <c r="D5" t="n">
-        <v>74.22</v>
+        <v>5198.76</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.9</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>72.56999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="G5" t="n">
-        <v>2.01</v>
+        <v>7.21</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5204.5</v>
+        <v>575.5</v>
       </c>
       <c r="D6" t="n">
-        <v>5198.76</v>
+        <v>510.94</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>12.6</v>
       </c>
       <c r="F6" t="n">
-        <v>67.16</v>
+        <v>62.09</v>
       </c>
       <c r="G6" t="n">
-        <v>7.21</v>
+        <v>3.06</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>575.5</v>
+        <v>68.37</v>
       </c>
       <c r="D7" t="n">
-        <v>510.94</v>
+        <v>74.22</v>
       </c>
       <c r="E7" t="n">
-        <v>12.6</v>
+        <v>-7.9</v>
       </c>
       <c r="F7" t="n">
-        <v>62.09</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.06</v>
+        <v>2.01</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>

--- a/output/2026-09-30/enriched_analysis.xlsx
+++ b/output/2026-09-30/enriched_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR52"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -889,25 +889,25 @@
         <v>87.19</v>
       </c>
       <c r="J2" t="n">
-        <v>75.34999999999999</v>
+        <v>75.77</v>
       </c>
       <c r="K2" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="L2" t="n">
         <v>61.32</v>
       </c>
       <c r="M2" t="n">
-        <v>96.02</v>
+        <v>88.06</v>
       </c>
       <c r="N2" t="n">
-        <v>960166595</v>
+        <v>880556810</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>960166595</v>
+        <v>880556810</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.314</v>
+        <v>3.011</v>
       </c>
       <c r="W2" t="n">
-        <v>2897</v>
+        <v>2924</v>
       </c>
       <c r="X2" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -971,10 +971,10 @@
         <v>151.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.35228891521577</v>
+        <v>75.76913270892582</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS2" t="n">
         <v>21</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="W3" t="n">
-        <v>2677</v>
+        <v>2711</v>
       </c>
       <c r="X3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.967</v>
       </c>
       <c r="W4" t="n">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="X4" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
@@ -1628,10 +1628,10 @@
         <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>16177</v>
+        <v>15973</v>
       </c>
       <c r="X5" t="n">
-        <v>41.2</v>
+        <v>40.6</v>
       </c>
       <c r="Y5" t="n">
         <v>83</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.31</v>
+        <v>0.311</v>
       </c>
       <c r="W6" t="n">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="X6" t="n">
-        <v>9.710000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.998</v>
+        <v>0.988</v>
       </c>
       <c r="W7" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="X7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2249,16 +2249,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2278,28 +2278,28 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>108.44</v>
+        <v>993.7</v>
       </c>
       <c r="J8" t="n">
-        <v>95.19</v>
+        <v>792.67</v>
       </c>
       <c r="K8" t="n">
-        <v>13.9</v>
+        <v>25.4</v>
       </c>
       <c r="L8" t="n">
-        <v>70.88</v>
+        <v>61.71</v>
       </c>
       <c r="M8" t="n">
-        <v>12.18</v>
+        <v>3.06</v>
       </c>
       <c r="N8" t="n">
-        <v>121849300</v>
+        <v>30643731</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>121849300</v>
+        <v>30643731</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2313,60 +2313,58 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.438</v>
+        <v>1.018</v>
       </c>
       <c r="W8" t="n">
-        <v>2785</v>
-      </c>
-      <c r="X8" t="n">
-        <v>22.8</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>11.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>-14</v>
+        <v>-184</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.57</v>
+        <v>31.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.9</v>
+        <v>-0.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>30</v>
+        <v>57.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>96.28</v>
+        <v>809.74</v>
       </c>
       <c r="AH8" t="n">
-        <v>92.5</v>
+        <v>785.61</v>
       </c>
       <c r="AI8" t="n">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>95.19335259867236</v>
+        <v>792.6674513050001</v>
       </c>
       <c r="AK8" t="n">
-        <v>13.9</v>
+        <v>25.4</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -2380,7 +2378,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2390,17 +2388,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AR8" t="n">
         <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
@@ -2409,28 +2407,28 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>17818369</v>
+        <v>1878236</v>
       </c>
       <c r="AZ8" t="n">
-        <v>36964024</v>
+        <v>9352142</v>
       </c>
       <c r="BA8" t="n">
-        <v>59380273</v>
+        <v>14526828</v>
       </c>
       <c r="BB8" t="n">
-        <v>121849300</v>
+        <v>30643731</v>
       </c>
       <c r="BC8" t="n">
-        <v>121849300</v>
+        <v>30643731</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -2463,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>17818369</v>
+        <v>1878236</v>
       </c>
       <c r="BO8" t="n">
-        <v>59380273</v>
+        <v>14526828</v>
       </c>
       <c r="BP8" t="n">
         <v>1</v>
@@ -2475,22 +2473,22 @@
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.3001</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2498,10 +2496,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2510,28 +2508,28 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>993.7</v>
+        <v>108.44</v>
       </c>
       <c r="J9" t="n">
-        <v>792.67</v>
+        <v>95.19</v>
       </c>
       <c r="K9" t="n">
-        <v>25.4</v>
+        <v>13.9</v>
       </c>
       <c r="L9" t="n">
-        <v>61.71</v>
+        <v>70.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.06</v>
+        <v>12.18</v>
       </c>
       <c r="N9" t="n">
-        <v>30643731</v>
+        <v>121849300</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30643731</v>
+        <v>121849300</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2545,58 +2543,60 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.995</v>
+        <v>0.44</v>
       </c>
       <c r="W9" t="n">
-        <v>308</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
+        <v>2771</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22.7</v>
+      </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.91</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>-184</v>
+        <v>-14</v>
       </c>
       <c r="AB9" t="n">
-        <v>31.98</v>
+        <v>0.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.26</v>
+        <v>16.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>57.93</v>
+        <v>30</v>
       </c>
       <c r="AG9" t="n">
-        <v>809.74</v>
+        <v>96.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>785.61</v>
+        <v>92.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>36.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>792.6674513050001</v>
+        <v>95.19335259867236</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.4</v>
+        <v>13.9</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -2620,17 +2620,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AR9" t="n">
         <v>44</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
@@ -2639,28 +2639,28 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1878236</v>
+        <v>17818369</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9352142</v>
+        <v>36964024</v>
       </c>
       <c r="BA9" t="n">
-        <v>14526828</v>
+        <v>59380273</v>
       </c>
       <c r="BB9" t="n">
-        <v>30643731</v>
+        <v>121849300</v>
       </c>
       <c r="BC9" t="n">
-        <v>30643731</v>
+        <v>121849300</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -2693,10 +2693,10 @@
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>1878236</v>
+        <v>17818369</v>
       </c>
       <c r="BO9" t="n">
-        <v>14526828</v>
+        <v>59380273</v>
       </c>
       <c r="BP9" t="n">
         <v>1</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.1293</v>
+        <v>0.3001</v>
       </c>
     </row>
     <row r="10">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2.334</v>
+        <v>2.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2515</v>
+        <v>2609</v>
       </c>
       <c r="X10" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="Y10" t="n">
         <v>6</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
-        <v>659</v>
+        <v>715</v>
       </c>
       <c r="X11" t="n">
-        <v>28.7</v>
+        <v>31.1</v>
       </c>
       <c r="Y11" t="n">
         <v>17</v>
@@ -3244,7 +3244,7 @@
         <v>0.116</v>
       </c>
       <c r="W12" t="n">
-        <v>2701</v>
+        <v>2711</v>
       </c>
       <c r="X12" t="n">
         <v>23.7</v>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="W13" t="n">
-        <v>1649</v>
+        <v>1685</v>
       </c>
       <c r="X13" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>2.86</v>
+        <v>2.881</v>
       </c>
       <c r="W14" t="n">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="X14" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="Y14" t="n">
         <v>30</v>
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="W15" t="n">
-        <v>1783</v>
+        <v>1801</v>
       </c>
       <c r="X15" t="n">
-        <v>40.9</v>
+        <v>41.3</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="X17" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="Y17" t="n">
         <v>19</v>
@@ -4585,25 +4585,25 @@
         <v>597.95</v>
       </c>
       <c r="J18" t="n">
-        <v>636.71</v>
+        <v>638.8200000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="L18" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>4.12</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>41238002</v>
+        <v>38328962</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>41238002</v>
+        <v>38328962</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.374</v>
+        <v>0.351</v>
       </c>
       <c r="W18" t="n">
-        <v>1104</v>
+        <v>1093</v>
       </c>
       <c r="X18" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4667,10 +4667,10 @@
         <v>35.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>636.7131718313339</v>
+        <v>638.8160333333333</v>
       </c>
       <c r="AK18" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AR18" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="AS18" t="n">
         <v>6</v>
@@ -4785,16 +4785,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
@@ -4814,28 +4814,28 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>77.43000000000001</v>
+        <v>448.2</v>
       </c>
       <c r="J19" t="n">
-        <v>81.09999999999999</v>
+        <v>489.56</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.5</v>
+        <v>-8.4</v>
       </c>
       <c r="L19" t="n">
-        <v>62.78</v>
+        <v>75</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>4.84</v>
       </c>
       <c r="N19" t="n">
-        <v>19959718</v>
+        <v>48436318</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>19959718</v>
+        <v>48436318</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -4849,64 +4849,64 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>53100</v>
+      </c>
+      <c r="X19" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>562</v>
+      </c>
+      <c r="AA19" t="n">
         <v>8</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="W19" t="n">
-        <v>397</v>
-      </c>
-      <c r="X19" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-19</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.54</v>
+        <v>3.16</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.73</v>
+        <v>22.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>41.64</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>77.84</v>
+        <v>498.99</v>
       </c>
       <c r="AH19" t="n">
-        <v>77.81</v>
+        <v>491.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>81.10277768748172</v>
+        <v>489.5623319654733</v>
       </c>
       <c r="AK19" t="n">
-        <v>-4.5</v>
+        <v>-8.4</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -4921,52 +4921,52 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1417187</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1417187</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>8313093</v>
+        <v>48436318</v>
       </c>
       <c r="BB19" t="n">
-        <v>19959718</v>
+        <v>48436318</v>
       </c>
       <c r="BC19" t="n">
-        <v>19959718</v>
+        <v>48436318</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -4999,34 +4999,34 @@
         <v>0</v>
       </c>
       <c r="BN19" t="n">
-        <v>1417187</v>
+        <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>8313093</v>
+        <v>48436318</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BQ19" t="n">
         <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>0.1705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
@@ -5046,28 +5046,28 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>448.2</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>489.56</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.4</v>
+        <v>-4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>75</v>
+        <v>62.78</v>
       </c>
       <c r="M20" t="n">
-        <v>4.84</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>48436318</v>
+        <v>19959718</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>48436318</v>
+        <v>19959718</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5081,124 +5081,124 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.497</v>
       </c>
       <c r="W20" t="n">
-        <v>52260</v>
+        <v>402</v>
       </c>
       <c r="X20" t="n">
-        <v>44.3</v>
+        <v>37.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>562</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AA20" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>81.10277768748172</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>28-08-2026</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>33</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW20" t="n">
         <v>8</v>
       </c>
-      <c r="AB20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>498.99</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>491.12</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>489.5623319654733</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5</v>
-      </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1417187</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1417187</v>
       </c>
       <c r="BA20" t="n">
-        <v>48436318</v>
+        <v>8313093</v>
       </c>
       <c r="BB20" t="n">
-        <v>48436318</v>
+        <v>19959718</v>
       </c>
       <c r="BC20" t="n">
-        <v>48436318</v>
+        <v>19959718</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5231,19 +5231,19 @@
         <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1417187</v>
       </c>
       <c r="BO20" t="n">
-        <v>48436318</v>
+        <v>8313093</v>
       </c>
       <c r="BP20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BQ20" t="n">
         <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="21">
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="W21" t="n">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="X21" t="n">
-        <v>51.8</v>
+        <v>53</v>
       </c>
       <c r="Y21" t="n">
         <v>3</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.91</v>
+        <v>0.922</v>
       </c>
       <c r="W22" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="X22" t="n">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
       <c r="Y22" t="n">
         <v>31</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="W23" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="X23" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.65</v>
+        <v>0.651</v>
       </c>
       <c r="W24" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="X24" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="Y24" t="n">
         <v>19</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.64</v>
+        <v>0.636</v>
       </c>
       <c r="W25" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="X25" t="n">
-        <v>1182</v>
+        <v>1192</v>
       </c>
       <c r="Y25" t="n">
         <v>-61</v>
@@ -6473,13 +6473,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.488</v>
+        <v>0.493</v>
       </c>
       <c r="W26" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="X26" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="Y26" t="n">
         <v>-44</v>
@@ -6708,7 +6708,7 @@
         <v>0.075</v>
       </c>
       <c r="W27" t="n">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -6938,7 +6938,7 @@
         <v>0.275</v>
       </c>
       <c r="W28" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="X28" t="n">
         <v>26.4</v>
@@ -7095,12 +7095,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7112,40 +7112,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>127.9</v>
+        <v>395.65</v>
       </c>
       <c r="J29" t="n">
-        <v>105.19</v>
+        <v>417.34</v>
       </c>
       <c r="K29" t="n">
-        <v>21.6</v>
+        <v>-5.2</v>
       </c>
       <c r="L29" t="n">
-        <v>67.15000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="M29" t="n">
-        <v>2.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>26297500</v>
+        <v>6931636</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>26297500</v>
+        <v>6931636</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7163,90 +7163,90 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.051</v>
+        <v>0.044</v>
       </c>
       <c r="W29" t="n">
-        <v>5163</v>
+        <v>1574</v>
       </c>
       <c r="X29" t="n">
-        <v>33.6</v>
+        <v>20.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.48</v>
+        <v>3.37</v>
       </c>
       <c r="AC29" t="n">
-        <v>10.7</v>
+        <v>23.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>114.62</v>
+        <v>432.34</v>
       </c>
       <c r="AH29" t="n">
-        <v>111.85</v>
+        <v>477.45</v>
       </c>
       <c r="AI29" t="n">
-        <v>43.9</v>
+        <v>-17.9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>105.19</v>
+        <v>417.3421638870492</v>
       </c>
       <c r="AK29" t="n">
-        <v>21.6</v>
+        <v>-5.2</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
@@ -7255,13 +7255,13 @@
         <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -7270,13 +7270,13 @@
         <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>6931636</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>6931636</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>6931636</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>6931636</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -7327,16 +7327,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7344,40 +7344,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>-3</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="I30" t="n">
-        <v>395.65</v>
+        <v>458.4</v>
       </c>
       <c r="J30" t="n">
-        <v>417.34</v>
+        <v>446.44</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.2</v>
+        <v>2.7</v>
       </c>
       <c r="L30" t="n">
-        <v>61.75</v>
+        <v>70.55</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6899999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="N30" t="n">
-        <v>6931636</v>
+        <v>315995072</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6931636</v>
+        <v>315995072</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7391,124 +7391,124 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.045</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="W30" t="n">
-        <v>1557</v>
+        <v>3894</v>
       </c>
       <c r="X30" t="n">
-        <v>20.3</v>
+        <v>27.2</v>
       </c>
       <c r="Y30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>440.07</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>432.15</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>446.4380077251934</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ30" t="n">
+        <v>54</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW30" t="n">
         <v>10</v>
       </c>
-      <c r="Z30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>432.34</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>477.45</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>-17.9</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>417.3421638870492</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1</v>
-      </c>
       <c r="AX30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>122601839</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>173213274</v>
       </c>
       <c r="BA30" t="n">
-        <v>6931636</v>
+        <v>213764169</v>
       </c>
       <c r="BB30" t="n">
-        <v>6931636</v>
+        <v>315995072</v>
       </c>
       <c r="BC30" t="n">
-        <v>6931636</v>
+        <v>315995072</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7541,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>122601839</v>
       </c>
       <c r="BO30" t="n">
-        <v>6931636</v>
+        <v>213764169</v>
       </c>
       <c r="BP30" t="n">
         <v>1</v>
@@ -7553,18 +7553,18 @@
         <v>0</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>0.5735</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7576,40 +7576,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="G31" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="I31" t="n">
-        <v>458.4</v>
+        <v>54.68</v>
       </c>
       <c r="J31" t="n">
-        <v>446.44</v>
+        <v>54.07</v>
       </c>
       <c r="K31" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="L31" t="n">
-        <v>70.55</v>
+        <v>67.23</v>
       </c>
       <c r="M31" t="n">
-        <v>31.6</v>
+        <v>2.2</v>
       </c>
       <c r="N31" t="n">
-        <v>315995072</v>
+        <v>21953383</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>315995072</v>
+        <v>21953383</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -7623,60 +7623,58 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.804</v>
+        <v>1.909</v>
       </c>
       <c r="W31" t="n">
-        <v>3931</v>
-      </c>
-      <c r="X31" t="n">
-        <v>27.5</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z31" t="n">
-        <v>127</v>
+        <v>2.47</v>
       </c>
       <c r="AA31" t="n">
-        <v>-14</v>
+        <v>-3779</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.41</v>
+        <v>-0.05</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.890000000000001</v>
+        <v>-1.26</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AG31" t="n">
-        <v>440.07</v>
+        <v>54.92</v>
       </c>
       <c r="AH31" t="n">
-        <v>432.15</v>
+        <v>55.24</v>
       </c>
       <c r="AI31" t="n">
-        <v>11.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ31" t="n">
-        <v>446.4380077251934</v>
+        <v>54.06877621438969</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -7700,47 +7698,47 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AR31" t="n">
         <v>56</v>
       </c>
       <c r="AS31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
         <v>2</v>
       </c>
-      <c r="AT31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4</v>
-      </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>122601839</v>
+        <v>1828800</v>
       </c>
       <c r="AZ31" t="n">
-        <v>173213274</v>
+        <v>2496120</v>
       </c>
       <c r="BA31" t="n">
-        <v>213764169</v>
+        <v>4318768</v>
       </c>
       <c r="BB31" t="n">
-        <v>315995072</v>
+        <v>21953383</v>
       </c>
       <c r="BC31" t="n">
-        <v>315995072</v>
+        <v>21953383</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
@@ -7773,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="BN31" t="n">
-        <v>122601839</v>
+        <v>1828800</v>
       </c>
       <c r="BO31" t="n">
-        <v>213764169</v>
+        <v>4318768</v>
       </c>
       <c r="BP31" t="n">
         <v>1</v>
@@ -7785,18 +7783,18 @@
         <v>0</v>
       </c>
       <c r="BR31" t="n">
-        <v>0.5735</v>
+        <v>0.4235</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -7808,109 +7806,111 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>153.08</v>
+      </c>
+      <c r="J32" t="n">
+        <v>176.53</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13998476</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13998476</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="W32" t="n">
+        <v>621</v>
+      </c>
+      <c r="X32" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Y32" t="n">
         <v>-1</v>
       </c>
-      <c r="I32" t="n">
-        <v>54.68</v>
-      </c>
-      <c r="J32" t="n">
-        <v>54.07</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>21953383</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>21953383</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>13</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>1.909</v>
-      </c>
-      <c r="W32" t="n">
-        <v>115</v>
-      </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="n">
-        <v>6</v>
-      </c>
       <c r="Z32" t="n">
-        <v>2.47</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>-3779</v>
+        <v>45</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>-1.26</v>
+        <v>19.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE32" t="b">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AG32" t="n">
-        <v>54.92</v>
+        <v>166.79</v>
       </c>
       <c r="AH32" t="n">
-        <v>55.24</v>
+        <v>189.67</v>
       </c>
       <c r="AI32" t="n">
-        <v>-1.2</v>
+        <v>-8.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>54.06877621438969</v>
+        <v>176.5255485498108</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.1</v>
+        <v>-13.3</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -7925,52 +7925,52 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="AR32" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="AS32" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW32" t="n">
         <v>2</v>
       </c>
-      <c r="AV32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>13</v>
-      </c>
       <c r="AX32" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AY32" t="n">
-        <v>1828800</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2496120</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>4318768</v>
+        <v>3009963</v>
       </c>
       <c r="BB32" t="n">
-        <v>21953383</v>
+        <v>8001009</v>
       </c>
       <c r="BC32" t="n">
-        <v>21953383</v>
+        <v>8001009</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8003,10 +8003,10 @@
         <v>0</v>
       </c>
       <c r="BN32" t="n">
-        <v>1828800</v>
+        <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>4318768</v>
+        <v>3009963</v>
       </c>
       <c r="BP32" t="n">
         <v>1</v>
@@ -8015,18 +8015,18 @@
         <v>0</v>
       </c>
       <c r="BR32" t="n">
-        <v>0.4235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -8038,40 +8038,40 @@
         </is>
       </c>
       <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="n">
         <v>4</v>
       </c>
-      <c r="F33" t="n">
-        <v>19</v>
-      </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>153.08</v>
+        <v>26.17</v>
       </c>
       <c r="J33" t="n">
-        <v>176.53</v>
+        <v>29.64</v>
       </c>
       <c r="K33" t="n">
-        <v>-13.3</v>
+        <v>-11.7</v>
       </c>
       <c r="L33" t="n">
-        <v>64.08</v>
+        <v>61.81</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4</v>
+        <v>0.74</v>
       </c>
       <c r="N33" t="n">
-        <v>13998476</v>
+        <v>7410250</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>13998476</v>
+        <v>7410250</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -8085,64 +8085,64 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.226</v>
+        <v>0.267</v>
       </c>
       <c r="W33" t="n">
-        <v>619</v>
+        <v>278</v>
       </c>
       <c r="X33" t="n">
-        <v>13.6</v>
+        <v>14.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>21</v>
+        <v>2.79</v>
       </c>
       <c r="AA33" t="n">
-        <v>45</v>
+        <v>-30</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.1</v>
+        <v>0.21</v>
       </c>
       <c r="AC33" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>11</v>
+        <v>1.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>166.79</v>
+        <v>28.08</v>
       </c>
       <c r="AH33" t="n">
-        <v>189.67</v>
+        <v>32</v>
       </c>
       <c r="AI33" t="n">
-        <v>-8.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ33" t="n">
-        <v>176.5255485498108</v>
+        <v>29.641</v>
       </c>
       <c r="AK33" t="n">
-        <v>-13.3</v>
+        <v>-11.7</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -8157,52 +8157,52 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="AR33" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AS33" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AX33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1331000</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>3342250</v>
       </c>
       <c r="BA33" t="n">
-        <v>3009963</v>
+        <v>3342250</v>
       </c>
       <c r="BB33" t="n">
-        <v>8001009</v>
+        <v>5545000</v>
       </c>
       <c r="BC33" t="n">
-        <v>8001009</v>
+        <v>5545000</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8235,10 +8235,10 @@
         <v>0</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1331000</v>
       </c>
       <c r="BO33" t="n">
-        <v>3009963</v>
+        <v>3342250</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
@@ -8247,22 +8247,22 @@
         <v>0</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>0.3982</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8270,40 +8270,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>26.17</v>
+        <v>191.48</v>
       </c>
       <c r="J34" t="n">
-        <v>29.64</v>
+        <v>191.87</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.7</v>
+        <v>-0.2</v>
       </c>
       <c r="L34" t="n">
-        <v>61.81</v>
+        <v>70.02</v>
       </c>
       <c r="M34" t="n">
-        <v>0.74</v>
+        <v>1.34</v>
       </c>
       <c r="N34" t="n">
-        <v>7410250</v>
+        <v>13430794</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7410250</v>
+        <v>13430794</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -8317,64 +8317,64 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.268</v>
+        <v>0.04</v>
       </c>
       <c r="W34" t="n">
-        <v>277</v>
+        <v>3387</v>
       </c>
       <c r="X34" t="n">
-        <v>14.6</v>
+        <v>20.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.79</v>
+        <v>51</v>
       </c>
       <c r="AA34" t="n">
-        <v>-30</v>
+        <v>-9</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.21</v>
+        <v>2.04</v>
       </c>
       <c r="AC34" t="n">
-        <v>18</v>
+        <v>20.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
-        <v>28.08</v>
+        <v>205.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>32</v>
+        <v>193.53</v>
       </c>
       <c r="AI34" t="n">
-        <v>-1.9</v>
+        <v>30.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>29.641</v>
+        <v>191.8684857142857</v>
       </c>
       <c r="AK34" t="n">
-        <v>-11.7</v>
+        <v>-0.2</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -8389,52 +8389,52 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="AR34" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="AS34" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>2</v>
       </c>
-      <c r="AU34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>5</v>
-      </c>
       <c r="AW34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>1331000</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3342250</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3342250</v>
+        <v>11966478</v>
       </c>
       <c r="BB34" t="n">
-        <v>5545000</v>
+        <v>13430794</v>
       </c>
       <c r="BC34" t="n">
-        <v>5545000</v>
+        <v>13430794</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -8467,34 +8467,34 @@
         <v>0</v>
       </c>
       <c r="BN34" t="n">
-        <v>1331000</v>
+        <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>3342250</v>
+        <v>11966478</v>
       </c>
       <c r="BP34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ34" t="n">
         <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>0.3982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -8502,40 +8502,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>191.48</v>
+        <v>156.71</v>
       </c>
       <c r="J35" t="n">
-        <v>191.87</v>
+        <v>159.62</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="L35" t="n">
-        <v>70.02</v>
+        <v>65.64</v>
       </c>
       <c r="M35" t="n">
-        <v>1.34</v>
+        <v>3.99</v>
       </c>
       <c r="N35" t="n">
-        <v>13430794</v>
+        <v>39906048</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>13430794</v>
+        <v>39906048</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -8549,60 +8549,60 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.04</v>
+        <v>0.228</v>
       </c>
       <c r="W35" t="n">
-        <v>3361</v>
+        <v>1752</v>
       </c>
       <c r="X35" t="n">
-        <v>19.9</v>
+        <v>18.6</v>
       </c>
       <c r="Y35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA35" t="n">
         <v>-4</v>
       </c>
-      <c r="Z35" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>-9</v>
-      </c>
       <c r="AB35" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>20.8</v>
+        <v>14.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AG35" t="n">
-        <v>205.2</v>
+        <v>176.48</v>
       </c>
       <c r="AH35" t="n">
-        <v>193.53</v>
+        <v>185.01</v>
       </c>
       <c r="AI35" t="n">
-        <v>30.5</v>
+        <v>-13.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>191.8684857142857</v>
+        <v>159.624192</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -8621,52 +8621,52 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
         <v>2</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
       </c>
       <c r="AV35" t="n">
         <v>2</v>
       </c>
       <c r="AW35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="BA35" t="n">
-        <v>11966478</v>
+        <v>39906048</v>
       </c>
       <c r="BB35" t="n">
-        <v>13430794</v>
+        <v>39906048</v>
       </c>
       <c r="BC35" t="n">
-        <v>13430794</v>
+        <v>39906048</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8702,10 +8702,10 @@
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>11966478</v>
+        <v>39906048</v>
       </c>
       <c r="BP35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ35" t="n">
         <v>0</v>
@@ -8717,16 +8717,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>Maharashtra Seamless Limited</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8734,171 +8734,171 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I36" t="n">
-        <v>156.71</v>
+        <v>721.85</v>
       </c>
       <c r="J36" t="n">
-        <v>159.62</v>
+        <v>618.78</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.8</v>
+        <v>16.7</v>
       </c>
       <c r="L36" t="n">
-        <v>65.64</v>
+        <v>67.86</v>
       </c>
       <c r="M36" t="n">
-        <v>3.99</v>
+        <v>102.7</v>
       </c>
       <c r="N36" t="n">
-        <v>39906048</v>
+        <v>1026988804</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1007459825</v>
       </c>
       <c r="P36" t="n">
-        <v>39906048</v>
+        <v>19528979</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S36" t="b">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.229</v>
+        <v>0.019</v>
       </c>
       <c r="W36" t="n">
-        <v>1739</v>
+        <v>10085</v>
       </c>
       <c r="X36" t="n">
-        <v>18.4</v>
+        <v>13.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="Z36" t="n">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="AA36" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.36</v>
+        <v>20.21</v>
       </c>
       <c r="AC36" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AG36" t="n">
-        <v>176.48</v>
+        <v>640.6900000000001</v>
       </c>
       <c r="AH36" t="n">
-        <v>185.01</v>
+        <v>597.3200000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>-13.4</v>
+        <v>24.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>159.624192</v>
+        <v>618.7797818882931</v>
       </c>
       <c r="AK36" t="n">
-        <v>-1.8</v>
+        <v>16.7</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="AS36" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>39906048</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>39906048</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>39906048</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>39906048</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
@@ -8934,13 +8934,13 @@
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>39906048</v>
+        <v>0</v>
       </c>
       <c r="BP36" t="n">
         <v>1</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR36" t="n">
         <v>0</v>
@@ -8949,188 +8949,182 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Maharashtra Seamless Limited</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>6</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N37" t="n">
+        <v>20159573</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>20159573</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>2.817550384346611</v>
+      </c>
+      <c r="AK37" t="n">
         <v>-1</v>
       </c>
-      <c r="F37" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" t="n">
-        <v>21</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I37" t="n">
-        <v>721.85</v>
-      </c>
-      <c r="J37" t="n">
-        <v>618.78</v>
-      </c>
-      <c r="K37" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="L37" t="n">
-        <v>67.86</v>
-      </c>
-      <c r="M37" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1026988804</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1007459825</v>
-      </c>
-      <c r="P37" t="n">
-        <v>19528979</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Net Buying with Selling</t>
-        </is>
-      </c>
-      <c r="S37" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>9672</v>
-      </c>
-      <c r="X37" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>-12</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>184</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>640.6900000000001</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>597.3200000000001</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>618.7797818882931</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>16.7</v>
-      </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="AS37" t="n">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -9163,34 +9157,34 @@
         <v>0</v>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>20159573</v>
       </c>
       <c r="BP37" t="n">
         <v>1</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9201,37 +9195,37 @@
         <v>6</v>
       </c>
       <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
         <v>-2</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" t="n">
-        <v>2.79</v>
+        <v>39.41</v>
       </c>
       <c r="J38" t="n">
-        <v>2.82</v>
+        <v>42.6</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.1</v>
+        <v>-7.5</v>
       </c>
       <c r="L38" t="n">
-        <v>64.45</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>20159573</v>
+        <v>13998766</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>20159573</v>
+        <v>13998766</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -9245,118 +9239,124 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="W38" t="n">
+        <v>391</v>
+      </c>
+      <c r="X38" t="n">
+        <v>96.7</v>
+      </c>
       <c r="Y38" t="n">
+        <v>246</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA38" t="n">
         <v>10</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>-86</v>
-      </c>
       <c r="AB38" t="n">
-        <v>-0.03</v>
+        <v>0.14</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>14.22</v>
+        <v>4.21</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.89</v>
+        <v>40.58</v>
       </c>
       <c r="AH38" t="n">
-        <v>3.19</v>
+        <v>39.8</v>
       </c>
       <c r="AI38" t="n">
-        <v>-4.8</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.817550384346611</v>
+        <v>42.60032805144139</v>
       </c>
       <c r="AK38" t="n">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR38" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="AS38" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW38" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AX38" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AY38" t="n">
-        <v>20159573</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>20159573</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>20159573</v>
+        <v>6317149</v>
       </c>
       <c r="BB38" t="n">
-        <v>20159573</v>
+        <v>13998766</v>
       </c>
       <c r="BC38" t="n">
-        <v>20159573</v>
+        <v>13998766</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
@@ -9389,10 +9389,10 @@
         <v>0</v>
       </c>
       <c r="BN38" t="n">
-        <v>20159573</v>
+        <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>20159573</v>
+        <v>6317149</v>
       </c>
       <c r="BP38" t="n">
         <v>1</v>
@@ -9401,194 +9401,192 @@
         <v>0</v>
       </c>
       <c r="BR38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>6</v>
       </c>
       <c r="F39" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>196.14</v>
+      </c>
+      <c r="J39" t="n">
+        <v>195.05</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
         <v>4</v>
       </c>
-      <c r="G39" t="n">
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4104</v>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>258</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>188.37</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>176.65</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>195.0500869565217</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU39" t="n">
         <v>4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>39.41</v>
-      </c>
-      <c r="J39" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>13998766</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>13998766</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>12</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="W39" t="n">
-        <v>390</v>
-      </c>
-      <c r="X39" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>246</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>42.60032805144139</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>41</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
       </c>
       <c r="AV39" t="n">
         <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AX39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>2763736</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>4486152</v>
       </c>
       <c r="BA39" t="n">
-        <v>6317149</v>
+        <v>4486152</v>
       </c>
       <c r="BB39" t="n">
-        <v>13998766</v>
+        <v>4486152</v>
       </c>
       <c r="BC39" t="n">
-        <v>13998766</v>
+        <v>4486152</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
@@ -9621,10 +9619,10 @@
         <v>0</v>
       </c>
       <c r="BN39" t="n">
-        <v>0</v>
+        <v>2763736</v>
       </c>
       <c r="BO39" t="n">
-        <v>6317149</v>
+        <v>4486152</v>
       </c>
       <c r="BP39" t="n">
         <v>1</v>
@@ -9633,295 +9631,295 @@
         <v>0</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>0.6161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>Savita Oil Technologies Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I40" t="n">
-        <v>78.76000000000001</v>
+        <v>717</v>
       </c>
       <c r="J40" t="n">
-        <v>91.22</v>
+        <v>726.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-13.7</v>
+        <v>-1.3</v>
       </c>
       <c r="L40" t="n">
-        <v>71.72</v>
+        <v>71.92</v>
       </c>
       <c r="M40" t="n">
-        <v>1.37</v>
+        <v>3.76</v>
       </c>
       <c r="N40" t="n">
-        <v>13682958</v>
+        <v>37641643</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="P40" t="n">
-        <v>13682958</v>
+        <v>214003</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S40" t="b">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1632</v>
+        <v>5053</v>
       </c>
       <c r="X40" t="n">
-        <v>29.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Z40" t="n">
-        <v>31</v>
+        <v>364</v>
       </c>
       <c r="AA40" t="n">
-        <v>8</v>
+        <v>204</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.9</v>
+        <v>42.63</v>
       </c>
       <c r="AC40" t="n">
-        <v>11.3</v>
+        <v>14</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AG40" t="n">
-        <v>87.15000000000001</v>
+        <v>687.96</v>
       </c>
       <c r="AH40" t="n">
-        <v>151.37</v>
+        <v>480.55</v>
       </c>
       <c r="AI40" t="n">
-        <v>-47.9</v>
+        <v>121.2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>91.21972</v>
+        <v>726.2520355006753</v>
       </c>
       <c r="AK40" t="n">
-        <v>-13.7</v>
+        <v>-1.3</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="AS40" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>37641643</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>37641643</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>37641643</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>37641643</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>37641643</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BL40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BM40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BN40" t="n">
-        <v>0</v>
+        <v>214003</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>214003</v>
       </c>
       <c r="BP40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I41" t="n">
-        <v>196.14</v>
+        <v>182.87</v>
       </c>
       <c r="J41" t="n">
-        <v>195.05</v>
+        <v>170.45</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="L41" t="n">
-        <v>60.6</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="N41" t="n">
-        <v>4486152</v>
+        <v>2560187</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4486152</v>
+        <v>2560187</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -9935,122 +9933,124 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.011</v>
+        <v>0.104</v>
       </c>
       <c r="W41" t="n">
-        <v>4158</v>
-      </c>
-      <c r="X41" t="inlineStr"/>
+        <v>245</v>
+      </c>
+      <c r="X41" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y41" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Z41" t="n">
-        <v>258</v>
+        <v>1.87</v>
       </c>
       <c r="AA41" t="n">
-        <v>30</v>
+        <v>-31</v>
       </c>
       <c r="AB41" t="n">
-        <v>-1.13</v>
+        <v>3.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.38</v>
+        <v>4.96</v>
       </c>
       <c r="AD41" t="n">
-        <v>10.11</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>61</v>
+        <v>2.97</v>
       </c>
       <c r="AG41" t="n">
-        <v>188.37</v>
+        <v>181.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>176.65</v>
+        <v>164.01</v>
       </c>
       <c r="AI41" t="n">
-        <v>38.3</v>
+        <v>50.3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>195.0500869565217</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AS41" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
         <v>2</v>
       </c>
-      <c r="AU41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>4</v>
-      </c>
       <c r="AW41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY41" t="n">
-        <v>2763736</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4486152</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>4486152</v>
+        <v>2560187</v>
       </c>
       <c r="BB41" t="n">
-        <v>4486152</v>
+        <v>2560187</v>
       </c>
       <c r="BC41" t="n">
-        <v>4486152</v>
+        <v>2560187</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -10083,142 +10083,142 @@
         <v>0</v>
       </c>
       <c r="BN41" t="n">
-        <v>2763736</v>
+        <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>4486152</v>
+        <v>2560187</v>
       </c>
       <c r="BP41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ41" t="n">
         <v>0</v>
       </c>
       <c r="BR41" t="n">
-        <v>0.6161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Savita Oil Technologies Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
+        <v>25</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="J42" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="K42" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="L42" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2018403</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2018403</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>17</v>
       </c>
-      <c r="H42" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I42" t="n">
-        <v>717</v>
-      </c>
-      <c r="J42" t="n">
-        <v>726.25</v>
-      </c>
-      <c r="K42" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="N42" t="n">
-        <v>37641643</v>
-      </c>
-      <c r="O42" t="n">
-        <v>37427640</v>
-      </c>
-      <c r="P42" t="n">
-        <v>214003</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>99.43000000000001</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Net Buying with Selling</t>
-        </is>
-      </c>
-      <c r="S42" t="b">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="W42" t="n">
-        <v>4916</v>
+        <v>179</v>
       </c>
       <c r="X42" t="n">
-        <v>11.5</v>
+        <v>41.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Z42" t="n">
-        <v>364</v>
+        <v>3.17</v>
       </c>
       <c r="AA42" t="n">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="AB42" t="n">
-        <v>42.63</v>
+        <v>0.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>14</v>
+        <v>8.76</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>25</v>
+        <v>14.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>687.96</v>
+        <v>23.46</v>
       </c>
       <c r="AH42" t="n">
-        <v>480.55</v>
+        <v>22.76</v>
       </c>
       <c r="AI42" t="n">
-        <v>121.2</v>
+        <v>76.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>726.2520355006753</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK42" t="n">
-        <v>-1.3</v>
+        <v>41.8</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
@@ -10227,163 +10227,163 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AR42" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="AS42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AV42" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AW42" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AX42" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AY42" t="n">
-        <v>37641643</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>37641643</v>
+        <v>1308280</v>
       </c>
       <c r="BA42" t="n">
-        <v>37641643</v>
+        <v>1457700</v>
       </c>
       <c r="BB42" t="n">
-        <v>37641643</v>
+        <v>2018403</v>
       </c>
       <c r="BC42" t="n">
-        <v>37641643</v>
+        <v>2018403</v>
       </c>
       <c r="BD42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI42" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BJ42" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BK42" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BL42" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BM42" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BN42" t="n">
-        <v>214003</v>
+        <v>0</v>
       </c>
       <c r="BO42" t="n">
-        <v>214003</v>
+        <v>1457700</v>
       </c>
       <c r="BP42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BQ42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>182.87</v>
+        <v>384.2</v>
       </c>
       <c r="J43" t="n">
-        <v>170.45</v>
+        <v>338.1</v>
       </c>
       <c r="K43" t="n">
-        <v>7.3</v>
+        <v>13.6</v>
       </c>
       <c r="L43" t="n">
-        <v>67.54000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="M43" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -10397,94 +10397,94 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.104</v>
+        <v>0.074</v>
       </c>
       <c r="W43" t="n">
-        <v>246</v>
+        <v>457</v>
       </c>
       <c r="X43" t="n">
-        <v>26.3</v>
+        <v>13.5</v>
       </c>
       <c r="Y43" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z43" t="n">
         <v>24</v>
       </c>
-      <c r="Z43" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AA43" t="n">
-        <v>-31</v>
+        <v>33</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.36</v>
+        <v>14.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.96</v>
+        <v>9.94</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.97</v>
+        <v>18</v>
       </c>
       <c r="AG43" t="n">
-        <v>181.35</v>
+        <v>364.32</v>
       </c>
       <c r="AH43" t="n">
-        <v>164.01</v>
+        <v>271.37</v>
       </c>
       <c r="AI43" t="n">
-        <v>50.3</v>
+        <v>91.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>170.4518641810919</v>
+        <v>338.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>7.3</v>
+        <v>13.6</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ43" t="n">
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AS43" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AT43" t="n">
         <v>0</v>
@@ -10493,13 +10493,13 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -10508,13 +10508,13 @@
         <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>2560187</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="BC43" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -10550,10 +10550,10 @@
         <v>0</v>
       </c>
       <c r="BO43" t="n">
-        <v>2560187</v>
+        <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ43" t="n">
         <v>0</v>
@@ -10565,16 +10565,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10582,40 +10582,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>33.39</v>
+        <v>20.77</v>
       </c>
       <c r="J44" t="n">
-        <v>23.55</v>
+        <v>21.01</v>
       </c>
       <c r="K44" t="n">
-        <v>41.8</v>
+        <v>-1.1</v>
       </c>
       <c r="L44" t="n">
-        <v>68.34</v>
+        <v>70.87</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -10629,124 +10629,120 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="W44" t="n">
-        <v>171</v>
+        <v>417</v>
       </c>
       <c r="X44" t="n">
-        <v>39.5</v>
+        <v>6.73</v>
       </c>
       <c r="Y44" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3.17</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.76</v>
+        <v>19.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="n">
-        <v>14.87</v>
-      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="n">
-        <v>23.46</v>
+        <v>19.65</v>
       </c>
       <c r="AH44" t="n">
-        <v>22.76</v>
+        <v>15.54</v>
       </c>
       <c r="AI44" t="n">
-        <v>76.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AJ44" t="n">
-        <v>23.5472893358377</v>
+        <v>21.00741139152052</v>
       </c>
       <c r="AK44" t="n">
-        <v>41.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ44" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR44" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AS44" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>1457700</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="BC44" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="BD44" t="n">
         <v>0</v>
@@ -10782,10 +10778,10 @@
         <v>0</v>
       </c>
       <c r="BO44" t="n">
-        <v>1457700</v>
+        <v>0</v>
       </c>
       <c r="BP44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ44" t="n">
         <v>0</v>
@@ -10797,16 +10793,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10814,40 +10810,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="G45" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>384.2</v>
+        <v>657.35</v>
       </c>
       <c r="J45" t="n">
-        <v>338.1</v>
+        <v>593.62</v>
       </c>
       <c r="K45" t="n">
-        <v>13.6</v>
+        <v>10.7</v>
       </c>
       <c r="L45" t="n">
-        <v>66.73</v>
+        <v>74.02</v>
       </c>
       <c r="M45" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="N45" t="n">
-        <v>3381000</v>
+        <v>2458195</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3381000</v>
+        <v>2458195</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -10861,69 +10857,67 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.075</v>
+        <v>0.024</v>
       </c>
       <c r="W45" t="n">
-        <v>453</v>
-      </c>
-      <c r="X45" t="n">
-        <v>13.4</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="Z45" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="n">
+        <v>-152</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>597.02</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>549.01</v>
+      </c>
+      <c r="AI45" t="n">
         <v>33</v>
       </c>
-      <c r="AB45" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>364.32</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>271.37</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>91.5</v>
-      </c>
       <c r="AJ45" t="n">
-        <v>338.1</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK45" t="n">
-        <v>13.6</v>
+        <v>10.7</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
@@ -10933,22 +10927,22 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR45" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="AS45" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="AT45" t="n">
         <v>0</v>
@@ -10957,13 +10951,13 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -10972,13 +10966,13 @@
         <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1288195</v>
       </c>
       <c r="BB45" t="n">
-        <v>3381000</v>
+        <v>2458195</v>
       </c>
       <c r="BC45" t="n">
-        <v>3381000</v>
+        <v>2458195</v>
       </c>
       <c r="BD45" t="n">
         <v>0</v>
@@ -11014,10 +11008,10 @@
         <v>0</v>
       </c>
       <c r="BO45" t="n">
-        <v>0</v>
+        <v>1288195</v>
       </c>
       <c r="BP45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ45" t="n">
         <v>0</v>
@@ -11029,16 +11023,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -11046,40 +11040,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>20.77</v>
+        <v>328.3</v>
       </c>
       <c r="J46" t="n">
-        <v>21.01</v>
+        <v>335.41</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.1</v>
+        <v>-2.1</v>
       </c>
       <c r="L46" t="n">
-        <v>70.87</v>
+        <v>68.48</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="N46" t="n">
-        <v>4960333</v>
+        <v>4081958</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4960333</v>
+        <v>4081958</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -11093,56 +11087,60 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.126</v>
+        <v>0.008</v>
       </c>
       <c r="W46" t="n">
-        <v>395</v>
+        <v>5368</v>
       </c>
       <c r="X46" t="n">
-        <v>6.38</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Y46" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z46" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>223</v>
+      </c>
       <c r="AA46" t="n">
-        <v>391</v>
+        <v>175</v>
       </c>
       <c r="AB46" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC46" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
+      <c r="AF46" t="n">
+        <v>7</v>
+      </c>
       <c r="AG46" t="n">
-        <v>19.65</v>
+        <v>362.78</v>
       </c>
       <c r="AH46" t="n">
-        <v>15.54</v>
+        <v>335.73</v>
       </c>
       <c r="AI46" t="n">
-        <v>64.59999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>21.00741139152052</v>
+        <v>335.4115036976171</v>
       </c>
       <c r="AK46" t="n">
-        <v>-1.1</v>
+        <v>-2.1</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -11161,22 +11159,22 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AQ46" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="AR46" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="AS46" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
@@ -11188,10 +11186,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -11203,10 +11201,10 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>4960333</v>
+        <v>1094828</v>
       </c>
       <c r="BC46" t="n">
-        <v>4960333</v>
+        <v>1094828</v>
       </c>
       <c r="BD46" t="n">
         <v>0</v>
@@ -11257,16 +11255,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11274,139 +11272,141 @@
         </is>
       </c>
       <c r="E47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>26</v>
+      </c>
+      <c r="G47" t="n">
         <v>5</v>
       </c>
-      <c r="F47" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>25</v>
-      </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I47" t="n">
-        <v>657.35</v>
+        <v>182.69</v>
       </c>
       <c r="J47" t="n">
-        <v>593.62</v>
+        <v>207.63</v>
       </c>
       <c r="K47" t="n">
-        <v>10.7</v>
+        <v>-12</v>
       </c>
       <c r="L47" t="n">
-        <v>74.02</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>0.25</v>
+        <v>4.7</v>
       </c>
       <c r="N47" t="n">
-        <v>2458195</v>
+        <v>46970458</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>46898837</v>
       </c>
       <c r="P47" t="n">
-        <v>2458195</v>
+        <v>71621</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S47" t="b">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1022</v>
-      </c>
-      <c r="X47" t="inlineStr"/>
+        <v>8896</v>
+      </c>
+      <c r="X47" t="n">
+        <v>15.1</v>
+      </c>
       <c r="Y47" t="n">
-        <v>-2</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="n">
-        <v>5</v>
+        <v>224</v>
       </c>
       <c r="AA47" t="n">
-        <v>-152</v>
+        <v>38</v>
       </c>
       <c r="AB47" t="n">
-        <v>-6.5</v>
+        <v>3.32</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.24</v>
+        <v>24.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.23</v>
+        <v>0.11</v>
       </c>
       <c r="AE47" t="b">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="AG47" t="n">
-        <v>597.02</v>
+        <v>198.08</v>
       </c>
       <c r="AH47" t="n">
-        <v>549.01</v>
+        <v>208.95</v>
       </c>
       <c r="AI47" t="n">
-        <v>33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ47" t="n">
-        <v>593.6235208886742</v>
+        <v>207.6336012165256</v>
       </c>
       <c r="AK47" t="n">
-        <v>10.7</v>
+        <v>-12</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AQ47" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="AS47" t="n">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="AT47" t="n">
         <v>0</v>
@@ -11415,13 +11415,13 @@
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -11430,13 +11430,13 @@
         <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
         <v>0</v>
@@ -11472,13 +11472,13 @@
         <v>0</v>
       </c>
       <c r="BO47" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="BP47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR47" t="n">
         <v>0</v>
@@ -11487,16 +11487,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -11504,213 +11504,213 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="I48" t="n">
-        <v>328.3</v>
+        <v>1653</v>
       </c>
       <c r="J48" t="n">
-        <v>335.41</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.1</v>
+        <v>109.3</v>
       </c>
       <c r="L48" t="n">
-        <v>68.48</v>
+        <v>67.55</v>
       </c>
       <c r="M48" t="n">
-        <v>0.41</v>
+        <v>12.76</v>
       </c>
       <c r="N48" t="n">
-        <v>4081958</v>
+        <v>127606073</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>130033072</v>
       </c>
       <c r="P48" t="n">
-        <v>4081958</v>
+        <v>-2426999</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>101.9</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Selling</t>
         </is>
       </c>
       <c r="S48" t="b">
         <v>0</v>
       </c>
       <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>3507</v>
+      </c>
+      <c r="X48" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1639.87</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1388.41</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>789.9446136512771</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>97</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>97</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP48" t="n">
         <v>2</v>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="W48" t="n">
-        <v>5381</v>
-      </c>
-      <c r="X48" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>223</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>175</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>362.78</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>335.73</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>335.4115036976171</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ48" t="n">
-        <v>49</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>92</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>43</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1094828</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>1094828</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP48" t="n">
-        <v>1</v>
-      </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR48" t="n">
         <v>0</v>
@@ -11719,16 +11719,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11736,141 +11736,141 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>5</v>
       </c>
       <c r="H49" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>182.69</v>
+        <v>110.81</v>
       </c>
       <c r="J49" t="n">
-        <v>207.63</v>
+        <v>111.01</v>
       </c>
       <c r="K49" t="n">
-        <v>-12</v>
+        <v>-0.2</v>
       </c>
       <c r="L49" t="n">
-        <v>74.26000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="M49" t="n">
-        <v>4.7</v>
+        <v>0.45</v>
       </c>
       <c r="N49" t="n">
-        <v>46970458</v>
+        <v>4484713</v>
       </c>
       <c r="O49" t="n">
-        <v>46898837</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>71621</v>
+        <v>4484713</v>
       </c>
       <c r="Q49" t="n">
-        <v>99.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Net Buying with Selling</t>
+          <t>Net Buying</t>
         </is>
       </c>
       <c r="S49" t="b">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="W49" t="n">
-        <v>8881</v>
+        <v>216</v>
       </c>
       <c r="X49" t="n">
-        <v>15.1</v>
+        <v>25.7</v>
       </c>
       <c r="Y49" t="n">
         <v>21</v>
       </c>
       <c r="Z49" t="n">
-        <v>224</v>
+        <v>12.07</v>
       </c>
       <c r="AA49" t="n">
-        <v>38</v>
+        <v>-29</v>
       </c>
       <c r="AB49" t="n">
-        <v>3.32</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
-        <v>24.2</v>
+        <v>7.92</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="AE49" t="b">
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>41</v>
+        <v>4.11</v>
       </c>
       <c r="AG49" t="n">
-        <v>198.08</v>
+        <v>112.08</v>
       </c>
       <c r="AH49" t="n">
-        <v>208.95</v>
+        <v>118.05</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>207.6336012165256</v>
+        <v>111.0077475247525</v>
       </c>
       <c r="AK49" t="n">
-        <v>-12</v>
+        <v>-0.2</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AR49" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="AS49" t="n">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="AT49" t="n">
         <v>0</v>
@@ -11879,13 +11879,13 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -11894,13 +11894,13 @@
         <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1226198</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>4484713</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>4484713</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
@@ -11936,13 +11936,13 @@
         <v>0</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>1226198</v>
       </c>
       <c r="BP49" t="n">
         <v>1</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR49" t="n">
         <v>0</v>
@@ -11951,16 +11951,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>JINDAL STEEL LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -11971,40 +11971,40 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="I50" t="n">
-        <v>1653</v>
+        <v>1130</v>
       </c>
       <c r="J50" t="n">
-        <v>789.9400000000001</v>
+        <v>1157.18</v>
       </c>
       <c r="K50" t="n">
-        <v>109.3</v>
+        <v>-2.3</v>
       </c>
       <c r="L50" t="n">
-        <v>67.55</v>
+        <v>61.21</v>
       </c>
       <c r="M50" t="n">
-        <v>12.76</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>127606073</v>
+        <v>92111332</v>
       </c>
       <c r="O50" t="n">
-        <v>130033072</v>
+        <v>108203920</v>
       </c>
       <c r="P50" t="n">
-        <v>-2426999</v>
+        <v>-16092588</v>
       </c>
       <c r="Q50" t="n">
-        <v>101.9</v>
+        <v>117.47</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -12015,94 +12015,94 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3449</v>
+        <v>115270</v>
       </c>
       <c r="X50" t="n">
-        <v>77.59999999999999</v>
+        <v>33.2</v>
       </c>
       <c r="Y50" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="Z50" t="n">
-        <v>13</v>
+        <v>2224</v>
       </c>
       <c r="AA50" t="n">
-        <v>22</v>
+        <v>-28</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.05</v>
+        <v>10.65</v>
       </c>
       <c r="AC50" t="n">
-        <v>19.9</v>
+        <v>10.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1120.89</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1134.73</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1157.177537688442</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
         <v>27</v>
       </c>
-      <c r="AG50" t="n">
-        <v>1639.87</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1388.41</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>789.9446136512771</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>97</v>
-      </c>
       <c r="AS50" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="AT50" t="n">
         <v>0</v>
@@ -12111,13 +12111,13 @@
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -12126,13 +12126,13 @@
         <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
@@ -12144,10 +12144,10 @@
         <v>0</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI50" t="n">
         <v>0</v>
@@ -12159,488 +12159,24 @@
         <v>0</v>
       </c>
       <c r="BL50" t="n">
-        <v>0</v>
+        <v>108203920</v>
       </c>
       <c r="BM50" t="n">
-        <v>0</v>
+        <v>108203920</v>
       </c>
       <c r="BN50" t="n">
         <v>0</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BP50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ50" t="n">
         <v>1</v>
       </c>
       <c r="BR50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>VSTL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>4</v>
-      </c>
-      <c r="F51" t="n">
-        <v>5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>110.81</v>
-      </c>
-      <c r="J51" t="n">
-        <v>111.01</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L51" t="n">
-        <v>73.48</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S51" t="b">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>8</v>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="W51" t="n">
-        <v>210</v>
-      </c>
-      <c r="X51" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>-29</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>112.08</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>111.0077475247525</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ51" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>1226198</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO51" t="n">
-        <v>1226198</v>
-      </c>
-      <c r="BP51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>JINDAL STEEL LIMITED</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>12</v>
-      </c>
-      <c r="G52" t="n">
-        <v>4</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1130</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1157.18</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="L52" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="M52" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="N52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="O52" t="n">
-        <v>108203920</v>
-      </c>
-      <c r="P52" t="n">
-        <v>-16092588</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>117.47</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Net Selling</t>
-        </is>
-      </c>
-      <c r="S52" t="b">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>115270</v>
-      </c>
-      <c r="X52" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2224</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1120.89</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1134.73</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1157.177537688442</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>108203920</v>
-      </c>
-      <c r="BM52" t="n">
-        <v>108203920</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12655,7 +12191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12731,19 +12267,19 @@
         <v>87.19</v>
       </c>
       <c r="D2" t="n">
-        <v>75.34999999999999</v>
+        <v>75.77</v>
       </c>
       <c r="E2" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="F2" t="n">
         <v>61.32</v>
       </c>
       <c r="G2" t="n">
-        <v>96.02</v>
+        <v>88.06</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -12929,70 +12465,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108.44</v>
+        <v>993.7</v>
       </c>
       <c r="D8" t="n">
-        <v>95.19</v>
+        <v>792.67</v>
       </c>
       <c r="E8" t="n">
-        <v>13.9</v>
+        <v>25.4</v>
       </c>
       <c r="F8" t="n">
-        <v>70.88</v>
+        <v>61.71</v>
       </c>
       <c r="G8" t="n">
-        <v>12.18</v>
+        <v>3.06</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>993.7</v>
+        <v>108.44</v>
       </c>
       <c r="D9" t="n">
-        <v>792.67</v>
+        <v>95.19</v>
       </c>
       <c r="E9" t="n">
-        <v>25.4</v>
+        <v>13.9</v>
       </c>
       <c r="F9" t="n">
-        <v>61.71</v>
+        <v>70.88</v>
       </c>
       <c r="G9" t="n">
-        <v>3.06</v>
+        <v>12.18</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -13291,19 +12827,19 @@
         <v>597.95</v>
       </c>
       <c r="D18" t="n">
-        <v>636.71</v>
+        <v>638.8200000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="F18" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>4.12</v>
+        <v>3.83</v>
       </c>
       <c r="H18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -13314,70 +12850,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77.43000000000001</v>
+        <v>448.2</v>
       </c>
       <c r="D19" t="n">
-        <v>81.09999999999999</v>
+        <v>489.56</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5</v>
+        <v>-8.4</v>
       </c>
       <c r="F19" t="n">
-        <v>62.78</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>4.84</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>448.2</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>489.56</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.4</v>
+        <v>-4.5</v>
       </c>
       <c r="F20" t="n">
-        <v>75</v>
+        <v>62.78</v>
       </c>
       <c r="G20" t="n">
-        <v>4.84</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -13664,838 +13200,768 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>127.9</v>
+        <v>395.65</v>
       </c>
       <c r="D29" t="n">
-        <v>105.19</v>
+        <v>417.34</v>
       </c>
       <c r="E29" t="n">
-        <v>21.6</v>
+        <v>-5.2</v>
       </c>
       <c r="F29" t="n">
-        <v>67.15000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="G29" t="n">
-        <v>2.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>395.65</v>
+        <v>458.4</v>
       </c>
       <c r="D30" t="n">
-        <v>417.34</v>
+        <v>446.44</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.2</v>
+        <v>2.7</v>
       </c>
       <c r="F30" t="n">
-        <v>61.75</v>
+        <v>70.55</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6899999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>458.4</v>
+        <v>54.68</v>
       </c>
       <c r="D31" t="n">
-        <v>446.44</v>
+        <v>54.07</v>
       </c>
       <c r="E31" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="F31" t="n">
-        <v>70.55</v>
+        <v>67.23</v>
       </c>
       <c r="G31" t="n">
-        <v>31.6</v>
+        <v>2.2</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>54.68</v>
+        <v>153.08</v>
       </c>
       <c r="D32" t="n">
-        <v>54.07</v>
+        <v>176.53</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1</v>
+        <v>-13.3</v>
       </c>
       <c r="F32" t="n">
-        <v>67.23</v>
+        <v>64.08</v>
       </c>
       <c r="G32" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>153.08</v>
+        <v>26.17</v>
       </c>
       <c r="D33" t="n">
-        <v>176.53</v>
+        <v>29.64</v>
       </c>
       <c r="E33" t="n">
-        <v>-13.3</v>
+        <v>-11.7</v>
       </c>
       <c r="F33" t="n">
-        <v>64.08</v>
+        <v>61.81</v>
       </c>
       <c r="G33" t="n">
-        <v>1.4</v>
+        <v>0.74</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>26.17</v>
+        <v>191.48</v>
       </c>
       <c r="D34" t="n">
-        <v>29.64</v>
+        <v>191.87</v>
       </c>
       <c r="E34" t="n">
-        <v>-11.7</v>
+        <v>-0.2</v>
       </c>
       <c r="F34" t="n">
-        <v>61.81</v>
+        <v>70.02</v>
       </c>
       <c r="G34" t="n">
-        <v>0.74</v>
+        <v>1.34</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>191.48</v>
+        <v>156.71</v>
       </c>
       <c r="D35" t="n">
-        <v>191.87</v>
+        <v>159.62</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="F35" t="n">
-        <v>70.02</v>
+        <v>65.64</v>
       </c>
       <c r="G35" t="n">
-        <v>1.34</v>
+        <v>3.99</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>Maharashtra Seamless Limited</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>156.71</v>
+        <v>721.85</v>
       </c>
       <c r="D36" t="n">
-        <v>159.62</v>
+        <v>618.78</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.8</v>
+        <v>16.7</v>
       </c>
       <c r="F36" t="n">
-        <v>65.64</v>
+        <v>67.86</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99</v>
+        <v>102.7</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Maharashtra Seamless Limited</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>721.85</v>
+        <v>2.79</v>
       </c>
       <c r="D37" t="n">
-        <v>618.78</v>
+        <v>2.82</v>
       </c>
       <c r="E37" t="n">
-        <v>16.7</v>
+        <v>-1.1</v>
       </c>
       <c r="F37" t="n">
-        <v>67.86</v>
+        <v>64.45</v>
       </c>
       <c r="G37" t="n">
-        <v>102.7</v>
+        <v>2.02</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.79</v>
+        <v>39.41</v>
       </c>
       <c r="D38" t="n">
-        <v>2.82</v>
+        <v>42.6</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1</v>
+        <v>-7.5</v>
       </c>
       <c r="F38" t="n">
-        <v>64.45</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>39.41</v>
+        <v>196.14</v>
       </c>
       <c r="D39" t="n">
-        <v>42.6</v>
+        <v>195.05</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.5</v>
+        <v>0.6</v>
       </c>
       <c r="F39" t="n">
-        <v>71.79000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="G39" t="n">
-        <v>1.4</v>
+        <v>0.45</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>Savita Oil Technologies Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>78.76000000000001</v>
+        <v>717</v>
       </c>
       <c r="D40" t="n">
-        <v>91.22</v>
+        <v>726.25</v>
       </c>
       <c r="E40" t="n">
-        <v>-13.7</v>
+        <v>-1.3</v>
       </c>
       <c r="F40" t="n">
-        <v>71.72</v>
+        <v>71.92</v>
       </c>
       <c r="G40" t="n">
-        <v>1.37</v>
+        <v>3.76</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>196.14</v>
+        <v>182.87</v>
       </c>
       <c r="D41" t="n">
-        <v>195.05</v>
+        <v>170.45</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="F41" t="n">
-        <v>60.6</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Savita Oil Technologies Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>717</v>
+        <v>33.39</v>
       </c>
       <c r="D42" t="n">
-        <v>726.25</v>
+        <v>23.55</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.3</v>
+        <v>41.8</v>
       </c>
       <c r="F42" t="n">
-        <v>71.92</v>
+        <v>68.34</v>
       </c>
       <c r="G42" t="n">
-        <v>3.76</v>
+        <v>0.2</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>182.87</v>
+        <v>384.2</v>
       </c>
       <c r="D43" t="n">
-        <v>170.45</v>
+        <v>338.1</v>
       </c>
       <c r="E43" t="n">
-        <v>7.3</v>
+        <v>13.6</v>
       </c>
       <c r="F43" t="n">
-        <v>67.54000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="G43" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33.39</v>
+        <v>20.77</v>
       </c>
       <c r="D44" t="n">
-        <v>23.55</v>
+        <v>21.01</v>
       </c>
       <c r="E44" t="n">
-        <v>41.8</v>
+        <v>-1.1</v>
       </c>
       <c r="F44" t="n">
-        <v>68.34</v>
+        <v>70.87</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>384.2</v>
+        <v>657.35</v>
       </c>
       <c r="D45" t="n">
-        <v>338.1</v>
+        <v>593.62</v>
       </c>
       <c r="E45" t="n">
-        <v>13.6</v>
+        <v>10.7</v>
       </c>
       <c r="F45" t="n">
-        <v>66.73</v>
+        <v>74.02</v>
       </c>
       <c r="G45" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>20.77</v>
+        <v>328.3</v>
       </c>
       <c r="D46" t="n">
-        <v>21.01</v>
+        <v>335.41</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.1</v>
+        <v>-2.1</v>
       </c>
       <c r="F46" t="n">
-        <v>70.87</v>
+        <v>68.48</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>657.35</v>
+        <v>182.69</v>
       </c>
       <c r="D47" t="n">
-        <v>593.62</v>
+        <v>207.63</v>
       </c>
       <c r="E47" t="n">
-        <v>10.7</v>
+        <v>-12</v>
       </c>
       <c r="F47" t="n">
-        <v>74.02</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>0.25</v>
+        <v>4.7</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>328.3</v>
+        <v>1653</v>
       </c>
       <c r="D48" t="n">
-        <v>335.41</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.1</v>
+        <v>109.3</v>
       </c>
       <c r="F48" t="n">
-        <v>68.48</v>
+        <v>67.55</v>
       </c>
       <c r="G48" t="n">
-        <v>0.41</v>
+        <v>12.76</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>182.69</v>
+        <v>110.81</v>
       </c>
       <c r="D49" t="n">
-        <v>207.63</v>
+        <v>111.01</v>
       </c>
       <c r="E49" t="n">
-        <v>-12</v>
+        <v>-0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>74.26000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="G49" t="n">
-        <v>4.7</v>
+        <v>0.45</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>JINDAL STEEL LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1653</v>
+        <v>1130</v>
       </c>
       <c r="D50" t="n">
-        <v>789.9400000000001</v>
+        <v>1157.18</v>
       </c>
       <c r="E50" t="n">
-        <v>109.3</v>
+        <v>-2.3</v>
       </c>
       <c r="F50" t="n">
-        <v>67.55</v>
+        <v>61.21</v>
       </c>
       <c r="G50" t="n">
-        <v>12.76</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>VSTL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>110.81</v>
-      </c>
-      <c r="D51" t="n">
-        <v>111.01</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>73.48</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H51" t="n">
-        <v>8</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>JINDAL STEEL LIMITED</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1130</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1157.18</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="F52" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="G52" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="inlineStr">
         <is>
           <t>03-09-2026</t>
         </is>
@@ -14544,7 +14010,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -14554,7 +14020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -14574,7 +14040,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -14584,7 +14050,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">

--- a/output/2026-09-30/enriched_analysis.xlsx
+++ b/output/2026-09-30/enriched_analysis.xlsx
@@ -1164,10 +1164,10 @@
         <v>0.049</v>
       </c>
       <c r="W3" t="n">
-        <v>2711</v>
+        <v>2727</v>
       </c>
       <c r="X3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1628,10 +1628,10 @@
         <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>15973</v>
+        <v>15905</v>
       </c>
       <c r="X5" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="Y5" t="n">
         <v>83</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.311</v>
+        <v>0.314</v>
       </c>
       <c r="W6" t="n">
-        <v>984</v>
+        <v>974</v>
       </c>
       <c r="X6" t="n">
-        <v>9.67</v>
+        <v>9.58</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.988</v>
+        <v>0.974</v>
       </c>
       <c r="W7" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="X7" t="n">
-        <v>8.630000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.018</v>
+        <v>1.001</v>
       </c>
       <c r="W8" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="W9" t="n">
-        <v>2771</v>
+        <v>2760</v>
       </c>
       <c r="X9" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>2.25</v>
+        <v>2.262</v>
       </c>
       <c r="W10" t="n">
-        <v>2609</v>
+        <v>2595</v>
       </c>
       <c r="X10" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Y10" t="n">
         <v>6</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="W11" t="n">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="X11" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="Y11" t="n">
         <v>17</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="W12" t="n">
-        <v>2711</v>
+        <v>2686</v>
       </c>
       <c r="X12" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Y12" t="n">
         <v>-3</v>
@@ -3476,10 +3476,10 @@
         <v>0.049</v>
       </c>
       <c r="W13" t="n">
-        <v>1685</v>
+        <v>1677</v>
       </c>
       <c r="X13" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>2.881</v>
+        <v>2.86</v>
       </c>
       <c r="W14" t="n">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="X14" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Y14" t="n">
         <v>30</v>
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="W15" t="n">
-        <v>1801</v>
+        <v>1768</v>
       </c>
       <c r="X15" t="n">
-        <v>41.3</v>
+        <v>40.6</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4166,7 +4166,7 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
@@ -4395,13 +4395,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="W17" t="n">
-        <v>820</v>
+        <v>837</v>
       </c>
       <c r="X17" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="Y17" t="n">
         <v>19</v>
@@ -4628,10 +4628,10 @@
         <v>0.351</v>
       </c>
       <c r="W18" t="n">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="X18" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4860,10 +4860,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>53100</v>
+        <v>52837</v>
       </c>
       <c r="X19" t="n">
-        <v>45</v>
+        <v>44.7</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.922</v>
+        <v>0.91</v>
       </c>
       <c r="W22" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="X22" t="n">
-        <v>6.3</v>
+        <v>6.37</v>
       </c>
       <c r="Y22" t="n">
         <v>31</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.31</v>
+        <v>0.315</v>
       </c>
       <c r="W23" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="X23" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.651</v>
+        <v>0.653</v>
       </c>
       <c r="W24" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="X24" t="n">
         <v>11.1</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.636</v>
+        <v>0.629</v>
       </c>
       <c r="W25" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="X25" t="n">
-        <v>1192</v>
+        <v>1204</v>
       </c>
       <c r="Y25" t="n">
         <v>-61</v>
@@ -6708,7 +6708,7 @@
         <v>0.075</v>
       </c>
       <c r="W27" t="n">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -7170,7 +7170,7 @@
         <v>0.044</v>
       </c>
       <c r="W29" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="X29" t="n">
         <v>20.6</v>
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="W30" t="n">
-        <v>3894</v>
+        <v>3850</v>
       </c>
       <c r="X30" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="Y30" t="n">
         <v>2</v>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>1.909</v>
+        <v>1.77</v>
       </c>
       <c r="W31" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
@@ -7861,13 +7861,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.225</v>
+        <v>0.227</v>
       </c>
       <c r="W32" t="n">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="X32" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="Y32" t="n">
         <v>-1</v>
@@ -8328,10 +8328,10 @@
         <v>0.04</v>
       </c>
       <c r="W34" t="n">
-        <v>3387</v>
+        <v>3371</v>
       </c>
       <c r="X34" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="n">
         <v>-4</v>
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="W35" t="n">
-        <v>1752</v>
+        <v>1739</v>
       </c>
       <c r="X35" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="Y35" t="n">
         <v>-3</v>
@@ -8792,7 +8792,7 @@
         <v>0.019</v>
       </c>
       <c r="W36" t="n">
-        <v>10085</v>
+        <v>10075</v>
       </c>
       <c r="X36" t="n">
         <v>13.3</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>5053</v>
+        <v>5071</v>
       </c>
       <c r="X40" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="Y40" t="n">
         <v>26</v>
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="W41" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="X41" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="Y41" t="n">
         <v>24</v>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="W45" t="n">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
@@ -11098,10 +11098,10 @@
         <v>0.008</v>
       </c>
       <c r="W46" t="n">
-        <v>5368</v>
+        <v>5316</v>
       </c>
       <c r="X46" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="Y46" t="n">
         <v>43</v>
@@ -11330,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>8896</v>
+        <v>8901</v>
       </c>
       <c r="X47" t="n">
         <v>15.1</v>
@@ -11562,10 +11562,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3507</v>
+        <v>3480</v>
       </c>
       <c r="X48" t="n">
-        <v>78.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="Y48" t="n">
         <v>42</v>
@@ -11791,13 +11791,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.208</v>
+        <v>0.21</v>
       </c>
       <c r="W49" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="X49" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="Y49" t="n">
         <v>21</v>
@@ -12026,10 +12026,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>115270</v>
+        <v>115066</v>
       </c>
       <c r="X50" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="Y50" t="n">
         <v>18</v>
